--- a/data/trans_dic/DC-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DC-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,55</t>
+          <t>2,83; 6,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,14</t>
+          <t>2,32; 5,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,97</t>
+          <t>0,52; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,62</t>
+          <t>3,88; 13,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,81; 24,99</t>
+          <t>17,59; 25,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 19,89</t>
+          <t>12,35; 19,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,04</t>
+          <t>7,04; 12,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 31,22</t>
+          <t>18,47; 30,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 14,7</t>
+          <t>10,6; 14,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,78</t>
+          <t>7,67; 11,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,23</t>
+          <t>4,11; 7,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 19,41</t>
+          <t>11,48; 19,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,97</t>
+          <t>6,84; 11,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,84</t>
+          <t>4,02; 7,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,74</t>
+          <t>2,2; 5,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 14,05</t>
+          <t>6,98; 13,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,54; 28,17</t>
+          <t>21,38; 28,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 17,38</t>
+          <t>11,83; 17,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 16,75</t>
+          <t>10,99; 16,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,97; 61,13</t>
+          <t>25,65; 62,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 18,01</t>
+          <t>14,23; 18,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,61</t>
+          <t>8,27; 11,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,12</t>
+          <t>7,02; 10,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,52; 43,04</t>
+          <t>17,65; 43,51</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,02; 18,62</t>
+          <t>12,86; 18,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,63</t>
+          <t>5,59; 9,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,44</t>
+          <t>5,33; 9,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 18,31</t>
+          <t>11,57; 17,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,56; 25,85</t>
+          <t>19,78; 26,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 23,5</t>
+          <t>17,21; 23,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,79</t>
+          <t>9,49; 14,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,47; 32,15</t>
+          <t>20,78; 31,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,98; 21,28</t>
+          <t>17,04; 21,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,83</t>
+          <t>12,18; 15,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,26</t>
+          <t>8,16; 11,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 24,0</t>
+          <t>18,34; 23,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 24,56</t>
+          <t>17,93; 24,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,2</t>
+          <t>7,65; 12,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,45</t>
+          <t>7,69; 12,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 24,95</t>
+          <t>7,68; 24,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 32,02</t>
+          <t>23,81; 31,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,81; 24,62</t>
+          <t>17,63; 24,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 20,29</t>
+          <t>14,25; 19,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 38,88</t>
+          <t>30,63; 39,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,52; 27,26</t>
+          <t>21,64; 26,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,63</t>
+          <t>13,25; 17,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 15,39</t>
+          <t>11,58; 15,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,47; 30,85</t>
+          <t>16,22; 31,17</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,95; 36,86</t>
+          <t>27,14; 36,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 17,19</t>
+          <t>10,01; 16,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 18,85</t>
+          <t>12,05; 18,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,82; 33,23</t>
+          <t>26,24; 33,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,56; 35,37</t>
+          <t>26,38; 35,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,43; 33,56</t>
+          <t>24,66; 33,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 28,89</t>
+          <t>21,24; 28,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,57; 46,96</t>
+          <t>40,79; 46,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,15; 34,59</t>
+          <t>28,43; 35,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 24,64</t>
+          <t>18,64; 24,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,46; 22,89</t>
+          <t>17,61; 22,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,28; 39,2</t>
+          <t>34,17; 39,35</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,62; 32,43</t>
+          <t>22,35; 32,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,22; 25,81</t>
+          <t>16,13; 25,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,99; 20,24</t>
+          <t>11,71; 19,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,99; 33,74</t>
+          <t>26,1; 33,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,88; 46,49</t>
+          <t>36,21; 46,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,34; 39,44</t>
+          <t>29,71; 39,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,36; 28,74</t>
+          <t>20,38; 29,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,53; 85,34</t>
+          <t>46,78; 84,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,2; 38,3</t>
+          <t>31,28; 38,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,51; 31,51</t>
+          <t>24,66; 31,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 23,38</t>
+          <t>17,2; 23,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,57; 74,15</t>
+          <t>38,45; 74,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,38; 43,73</t>
+          <t>30,57; 43,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,6; 31,7</t>
+          <t>20,19; 32,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 27,67</t>
+          <t>18,13; 27,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,45; 46,09</t>
+          <t>37,25; 46,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,97; 42,63</t>
+          <t>31,89; 43,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,74; 48,0</t>
+          <t>37,93; 48,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,92; 37,78</t>
+          <t>27,75; 37,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,67; 62,56</t>
+          <t>55,64; 62,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,71; 41,29</t>
+          <t>32,9; 41,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,96; 39,8</t>
+          <t>32,44; 40,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,83; 32,52</t>
+          <t>24,96; 32,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,08; 54,63</t>
+          <t>49,32; 54,71</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,89</t>
+          <t>16,25; 18,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,45</t>
+          <t>9,39; 11,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,43; 10,62</t>
+          <t>8,48; 10,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,15; 22,37</t>
+          <t>15,66; 22,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,44; 29,57</t>
+          <t>26,28; 29,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,43; 25,34</t>
+          <t>22,35; 25,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,94; 19,61</t>
+          <t>17,1; 19,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,77; 52,97</t>
+          <t>37,87; 52,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,7; 23,79</t>
+          <t>21,75; 23,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,24; 18,14</t>
+          <t>16,34; 18,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,14; 14,85</t>
+          <t>13,19; 14,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,45; 38,85</t>
+          <t>28,53; 37,95</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico</t>
+          <t>Población con dolor crónico (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13519; 32361</t>
+          <t>13978; 31801</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9869; 27886</t>
+          <t>10516; 27213</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2064; 12470</t>
+          <t>2173; 13032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15927; 58463</t>
+          <t>15509; 55506</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>83279; 116846</t>
+          <t>82219; 118616</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54355; 85576</t>
+          <t>53154; 83317</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29131; 51618</t>
+          <t>27876; 51314</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57404; 97771</t>
+          <t>57839; 96444</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100643; 141346</t>
+          <t>101905; 141957</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68925; 104146</t>
+          <t>67847; 103482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33851; 58979</t>
+          <t>33475; 60005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79700; 138417</t>
+          <t>81909; 139183</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49487; 80659</t>
+          <t>50282; 83116</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27657; 53876</t>
+          <t>27634; 52549</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13346; 33896</t>
+          <t>12967; 33892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28506; 59522</t>
+          <t>29543; 59021</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134754; 176207</t>
+          <t>133757; 176454</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71013; 106084</t>
+          <t>72197; 109449</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61440; 94385</t>
+          <t>61917; 94688</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>127879; 313067</t>
+          <t>131363; 322075</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>191573; 245061</t>
+          <t>193720; 250335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107501; 150685</t>
+          <t>107241; 151372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78973; 116794</t>
+          <t>81060; 119632</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163947; 402653</t>
+          <t>165130; 407097</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83126; 118923</t>
+          <t>82152; 116457</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38118; 65662</t>
+          <t>38104; 65921</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34513; 63176</t>
+          <t>35636; 63329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62140; 98188</t>
+          <t>62051; 95512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>134887; 178272</t>
+          <t>136439; 182809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>123733; 167035</t>
+          <t>122353; 165591</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65330; 97813</t>
+          <t>62769; 98048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>127128; 190302</t>
+          <t>123024; 188699</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>225528; 282656</t>
+          <t>226400; 281195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169011; 220429</t>
+          <t>169584; 222318</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106278; 149867</t>
+          <t>108601; 153422</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>202031; 270808</t>
+          <t>206969; 269040</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91571; 127504</t>
+          <t>93071; 128576</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45801; 74987</t>
+          <t>47040; 78934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47742; 80439</t>
+          <t>49709; 82106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64750; 221531</t>
+          <t>68203; 221758</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>123382; 165133</t>
+          <t>122771; 161943</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109763; 151730</t>
+          <t>108624; 151512</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91153; 131666</t>
+          <t>92479; 129438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>214847; 277139</t>
+          <t>218369; 279185</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222714; 282080</t>
+          <t>223931; 279051</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163992; 216981</t>
+          <t>163123; 217538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149725; 199350</t>
+          <t>149997; 200809</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>231602; 493771</t>
+          <t>259605; 498870</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>104218; 142541</t>
+          <t>104971; 140586</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>44223; 73828</t>
+          <t>42974; 72851</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57874; 90075</t>
+          <t>57566; 89464</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144911; 186518</t>
+          <t>147251; 187554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>107284; 142892</t>
+          <t>106552; 142411</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109386; 150280</t>
+          <t>110408; 150062</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>104113; 143519</t>
+          <t>105539; 142708</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>222261; 257318</t>
+          <t>223517; 257382</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>222612; 273497</t>
+          <t>224825; 277674</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164019; 216136</t>
+          <t>163549; 212586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170159; 223076</t>
+          <t>171626; 223551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>380190; 434830</t>
+          <t>378992; 436479</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66197; 94878</t>
+          <t>65405; 95731</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50263; 79962</t>
+          <t>49961; 80231</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40070; 67660</t>
+          <t>39135; 65258</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95680; 124204</t>
+          <t>96093; 123490</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>126487; 159413</t>
+          <t>124160; 159033</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>103858; 139608</t>
+          <t>105155; 141218</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76895; 108571</t>
+          <t>76993; 112309</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>283098; 519179</t>
+          <t>284612; 512487</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>198302; 243433</t>
+          <t>198809; 245788</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>162718; 209185</t>
+          <t>163716; 210806</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121249; 166458</t>
+          <t>122491; 167114</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>376617; 724139</t>
+          <t>375525; 725401</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>63766; 91790</t>
+          <t>64169; 91406</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51463; 79194</t>
+          <t>50434; 80913</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46803; 71115</t>
+          <t>46595; 70715</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105898; 130329</t>
+          <t>105330; 130219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106755; 142351</t>
+          <t>106481; 143840</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>146795; 186697</t>
+          <t>147522; 188713</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>111724; 151192</t>
+          <t>111060; 151422</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>237069; 266385</t>
+          <t>236937; 266323</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>177855; 224554</t>
+          <t>178881; 223356</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204156; 254244</t>
+          <t>207244; 258666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163170; 213723</t>
+          <t>164037; 214309</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>347759; 387110</t>
+          <t>349451; 387659</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>534641; 619071</t>
+          <t>532336; 618642</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>322100; 392294</t>
+          <t>321648; 393929</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>286053; 360552</t>
+          <t>287743; 357414</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>558646; 774040</t>
+          <t>541691; 774077</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>893553; 999137</t>
+          <t>887963; 995197</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>798128; 901736</t>
+          <t>795179; 899494</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>600473; 694991</t>
+          <t>606242; 705030</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1402061; 1966429</t>
+          <t>1405779; 1954309</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1444561; 1583231</t>
+          <t>1447744; 1578929</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1134634; 1266868</t>
+          <t>1141083; 1274004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>911753; 1030591</t>
+          <t>915013; 1032720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2040610; 2786276</t>
+          <t>2046408; 2721471</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC-Edad-trans_dic.xlsx
+++ b/data/trans_dic/DC-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,44</t>
+          <t>2,7; 6,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,99</t>
+          <t>2,26; 6,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,11</t>
+          <t>0,53; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,88</t>
+          <t>4,4; 13,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 25,37</t>
+          <t>17,7; 25,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,35; 19,37</t>
+          <t>12,64; 19,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 12,97</t>
+          <t>7,33; 13,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 30,79</t>
+          <t>18,53; 31,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,76</t>
+          <t>10,43; 14,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 11,7</t>
+          <t>7,72; 11,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 7,36</t>
+          <t>4,16; 7,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,52</t>
+          <t>12,49; 20,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,3</t>
+          <t>6,89; 10,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,65</t>
+          <t>4,2; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,74</t>
+          <t>2,28; 5,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 13,93</t>
+          <t>7,03; 14,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,38; 28,21</t>
+          <t>21,49; 28,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,93</t>
+          <t>11,92; 18,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,8</t>
+          <t>11,07; 16,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,65; 62,89</t>
+          <t>21,84; 30,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 18,39</t>
+          <t>14,29; 18,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,67</t>
+          <t>8,35; 11,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,37</t>
+          <t>7,0; 10,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 43,51</t>
+          <t>15,41; 20,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 18,23</t>
+          <t>12,91; 18,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,67</t>
+          <t>5,47; 9,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,46</t>
+          <t>5,2; 9,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 17,81</t>
+          <t>10,88; 16,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 26,5</t>
+          <t>19,51; 26,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 23,29</t>
+          <t>17,05; 23,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,82</t>
+          <t>9,98; 15,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,78; 31,87</t>
+          <t>27,73; 34,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,04; 21,17</t>
+          <t>17,01; 21,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 15,96</t>
+          <t>12,18; 16,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,53</t>
+          <t>8,1; 11,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 23,84</t>
+          <t>20,33; 24,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,93; 24,77</t>
+          <t>17,68; 24,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,84</t>
+          <t>7,45; 12,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,71</t>
+          <t>7,65; 12,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 24,98</t>
+          <t>19,99; 26,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 31,41</t>
+          <t>23,61; 31,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 24,59</t>
+          <t>17,58; 24,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 19,94</t>
+          <t>14,06; 19,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,63; 39,16</t>
+          <t>34,72; 40,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,97</t>
+          <t>21,88; 27,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,67</t>
+          <t>13,34; 17,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,5</t>
+          <t>11,64; 15,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,22; 31,17</t>
+          <t>28,53; 33,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,14; 36,35</t>
+          <t>27,61; 37,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,96</t>
+          <t>10,36; 16,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,72</t>
+          <t>11,96; 19,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,24; 33,42</t>
+          <t>25,45; 32,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,38; 35,25</t>
+          <t>26,16; 35,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 33,51</t>
+          <t>24,54; 33,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 28,72</t>
+          <t>20,7; 29,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,79; 46,98</t>
+          <t>41,15; 47,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,43; 35,12</t>
+          <t>28,28; 34,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,64; 24,23</t>
+          <t>18,65; 24,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,93</t>
+          <t>17,42; 22,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,17; 39,35</t>
+          <t>34,22; 39,08</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,35; 32,72</t>
+          <t>22,52; 32,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 25,9</t>
+          <t>16,64; 25,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,52</t>
+          <t>11,71; 19,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,1; 33,54</t>
+          <t>25,7; 33,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,21; 46,37</t>
+          <t>36,47; 45,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,71; 39,89</t>
+          <t>29,74; 39,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,38; 29,73</t>
+          <t>19,98; 28,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,78; 84,24</t>
+          <t>45,55; 52,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,28; 38,68</t>
+          <t>31,62; 38,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,66; 31,76</t>
+          <t>24,76; 31,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,2; 23,47</t>
+          <t>17,54; 23,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,45; 74,28</t>
+          <t>37,22; 42,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,57; 43,55</t>
+          <t>31,23; 43,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,19; 32,38</t>
+          <t>20,0; 31,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,13; 27,52</t>
+          <t>17,77; 27,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,25; 46,05</t>
+          <t>37,45; 46,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,89; 43,08</t>
+          <t>32,23; 42,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,93; 48,52</t>
+          <t>37,67; 48,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,75; 37,84</t>
+          <t>27,04; 37,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,64; 62,54</t>
+          <t>56,4; 62,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,9; 41,07</t>
+          <t>32,96; 41,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,44; 40,49</t>
+          <t>32,32; 40,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,96; 32,61</t>
+          <t>25,32; 32,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,32; 54,71</t>
+          <t>49,66; 55,28</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,25; 18,88</t>
+          <t>16,27; 19,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,5</t>
+          <t>9,21; 11,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 10,53</t>
+          <t>8,54; 10,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,66; 22,37</t>
+          <t>20,0; 23,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,28; 29,45</t>
+          <t>26,41; 29,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,35; 25,28</t>
+          <t>22,37; 25,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,1; 19,89</t>
+          <t>17,06; 19,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,87; 52,64</t>
+          <t>37,36; 40,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,75; 23,72</t>
+          <t>21,63; 23,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 18,24</t>
+          <t>16,26; 18,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13,19; 14,88</t>
+          <t>13,27; 14,91</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,53; 37,95</t>
+          <t>29,32; 31,43</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>33334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75647</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>106938</t>
+          <t>123113</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13978; 31801</t>
+          <t>13337; 31815</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10516; 27213</t>
+          <t>10281; 27350</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2173; 13032</t>
+          <t>2241; 13001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15509; 55506</t>
+          <t>17931; 56970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82219; 118616</t>
+          <t>82757; 116974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53154; 83317</t>
+          <t>54373; 85163</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27876; 51314</t>
+          <t>29003; 53315</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57839; 96444</t>
+          <t>67158; 114759</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>101905; 141957</t>
+          <t>100289; 139331</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67847; 103482</t>
+          <t>68246; 103257</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33475; 60005</t>
+          <t>33907; 60042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81909; 139183</t>
+          <t>96231; 159960</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>187493</t>
+          <t>128614</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>229627</t>
+          <t>176539</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50282; 83116</t>
+          <t>50658; 80704</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27634; 52549</t>
+          <t>28832; 52331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12967; 33892</t>
+          <t>13476; 33983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29543; 59021</t>
+          <t>33543; 67284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>133757; 176454</t>
+          <t>134436; 179825</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72197; 109449</t>
+          <t>72742; 111018</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61917; 94688</t>
+          <t>62400; 94037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>131363; 322075</t>
+          <t>109559; 150754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>193720; 250335</t>
+          <t>194513; 249353</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107241; 151372</t>
+          <t>108325; 152155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81060; 119632</t>
+          <t>80743; 119371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>165130; 407097</t>
+          <t>150849; 205292</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77805</t>
+          <t>85519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>192323</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>243535</t>
+          <t>277841</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82152; 116457</t>
+          <t>82424; 118929</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38104; 65921</t>
+          <t>37273; 65926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35636; 63329</t>
+          <t>34779; 62653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62051; 95512</t>
+          <t>67559; 104393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>136439; 182809</t>
+          <t>134593; 180454</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>122353; 165591</t>
+          <t>121218; 167308</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62769; 98048</t>
+          <t>66024; 100309</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123024; 188699</t>
+          <t>172793; 212021</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>226400; 281195</t>
+          <t>225979; 285688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169584; 222318</t>
+          <t>169613; 223657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108601; 153422</t>
+          <t>107759; 154256</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>206969; 269040</t>
+          <t>252856; 304928</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153286</t>
+          <t>163571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>253438</t>
+          <t>276660</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>406724</t>
+          <t>440231</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93071; 128576</t>
+          <t>91801; 128852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47040; 78934</t>
+          <t>45781; 76815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49709; 82106</t>
+          <t>49428; 80111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68203; 221758</t>
+          <t>140088; 187798</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122771; 161943</t>
+          <t>121741; 161757</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108624; 151512</t>
+          <t>108332; 152250</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92479; 129438</t>
+          <t>91281; 128759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>218369; 279185</t>
+          <t>255840; 297639</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223931; 279051</t>
+          <t>226418; 280755</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163123; 217538</t>
+          <t>164190; 215306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149997; 200809</t>
+          <t>150733; 200971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>259605; 498870</t>
+          <t>410151; 475139</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167079</t>
+          <t>176325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>240890</t>
+          <t>269048</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>407969</t>
+          <t>445374</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>104971; 140586</t>
+          <t>106790; 143737</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>42974; 72851</t>
+          <t>44504; 71311</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57566; 89464</t>
+          <t>57179; 90995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147251; 187554</t>
+          <t>155085; 197464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>106552; 142411</t>
+          <t>105690; 144321</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>110408; 150062</t>
+          <t>109911; 149476</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>105539; 142708</t>
+          <t>102848; 144525</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>223517; 257382</t>
+          <t>250549; 286698</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>224825; 277674</t>
+          <t>223601; 275698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163549; 212586</t>
+          <t>163635; 211846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171626; 223551</t>
+          <t>169772; 222482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>378992; 436479</t>
+          <t>416918; 476026</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>109663</t>
+          <t>120491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>397289</t>
+          <t>214886</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>506952</t>
+          <t>335377</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>65405; 95731</t>
+          <t>65885; 95140</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49961; 80231</t>
+          <t>51547; 79525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39135; 65258</t>
+          <t>39163; 66181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96093; 123490</t>
+          <t>104633; 136736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>124160; 159033</t>
+          <t>125075; 157137</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105155; 141218</t>
+          <t>105281; 139670</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76993; 112309</t>
+          <t>75492; 109433</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>284612; 512487</t>
+          <t>200058; 230097</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>198809; 245788</t>
+          <t>200966; 245339</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>163716; 210806</t>
+          <t>164346; 210801</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122491; 167114</t>
+          <t>124909; 165378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>375525; 725401</t>
+          <t>314935; 359231</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117431</t>
+          <t>130245</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>251686</t>
+          <t>277555</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>369117</t>
+          <t>407800</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>64169; 91406</t>
+          <t>65542; 91045</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>50434; 80913</t>
+          <t>49973; 78627</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46595; 70715</t>
+          <t>45680; 71277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105330; 130219</t>
+          <t>116181; 144857</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106481; 143840</t>
+          <t>107618; 143408</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>147522; 188713</t>
+          <t>146526; 187907</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>111060; 151422</t>
+          <t>108205; 149392</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>236937; 266323</t>
+          <t>262050; 292441</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>178881; 223356</t>
+          <t>179259; 225843</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>207244; 258666</t>
+          <t>206472; 255895</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164037; 214309</t>
+          <t>166376; 215766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>349451; 387659</t>
+          <t>384771; 428276</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>698690</t>
+          <t>757410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1572173</t>
+          <t>1448866</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2270863</t>
+          <t>2206276</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>532336; 618642</t>
+          <t>533223; 622922</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>321648; 393929</t>
+          <t>315704; 391960</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>287743; 357414</t>
+          <t>289786; 359789</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>541691; 774077</t>
+          <t>706662; 812902</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>887963; 995197</t>
+          <t>892353; 999527</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>795179; 899494</t>
+          <t>795910; 895993</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>606242; 705030</t>
+          <t>604553; 701740</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1405779; 1954309</t>
+          <t>1396088; 1501379</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1447744; 1578929</t>
+          <t>1439946; 1579800</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1141083; 1274004</t>
+          <t>1135931; 1268886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>915013; 1032720</t>
+          <t>920510; 1034593</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2046408; 2721471</t>
+          <t>2131668; 2284908</t>
         </is>
       </c>
     </row>
